--- a/buckman/output/ingested_data/2024/2024_Table_1_updated.xlsx
+++ b/buckman/output/ingested_data/2024/2024_Table_1_updated.xlsx
@@ -2176,9 +2176,8 @@
       <c r="N38" s="10" t="n">
         <v>212.018667</v>
       </c>
-      <c r="O38" s="10">
-        <f>SUM(B38:N38)</f>
-        <v/>
+      <c r="O38" s="10" t="n">
+        <v>1372.924212</v>
       </c>
       <c r="T38" s="10" t="n">
         <v>314.09</v>
